--- a/data/trans_camb/P38C-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Edad-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 1,93</t>
+          <t>-17,5; 2,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 4,26</t>
+          <t>-13,2; 3,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -0,45</t>
+          <t>-14,13; -0,26</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 4,07</t>
+          <t>-29,82; 5,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 6,9</t>
+          <t>-19,54; 6,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -0,67</t>
+          <t>-22,96; -0,49</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 3,57</t>
+          <t>-9,89; 4,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-40,47; -3,63</t>
+          <t>-41,29; -3,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,59; -2,38</t>
+          <t>-26,47; -2,07</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 5,41</t>
+          <t>-14,0; 6,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,84; -4,64</t>
+          <t>-50,2; -4,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -3,23</t>
+          <t>-35,9; -2,86</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 0,74</t>
+          <t>-8,61; 1,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,97</t>
+          <t>-4,64; 2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 0,84</t>
+          <t>-5,53; 0,49</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 0,95</t>
+          <t>-10,49; 1,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,57</t>
+          <t>-5,32; 3,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,04</t>
+          <t>-6,58; 0,59</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-60,16; 0,18</t>
+          <t>-61,64; 0,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 3,75</t>
+          <t>-2,47; 4,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 0,7</t>
+          <t>-39,66; 0,92</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 0,21</t>
+          <t>-70,04; 0,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,28</t>
+          <t>-2,69; 4,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 0,75</t>
+          <t>-44,52; 1,04</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,03</t>
+          <t>-3,61; 3,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,73</t>
+          <t>-2,16; 3,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,5</t>
+          <t>-1,95; 2,69</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,35</t>
+          <t>-3,81; 3,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,12</t>
+          <t>-2,28; 3,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,74</t>
+          <t>-2,08; 2,98</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,59</t>
+          <t>-4,23; 0,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,88</t>
+          <t>-1,81; 2,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,54</t>
+          <t>-2,19; 1,47</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,61</t>
+          <t>-4,31; 0,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,0</t>
+          <t>-1,83; 2,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,59</t>
+          <t>-2,25; 1,51</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,26</t>
+          <t>-0,81; 3,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,16</t>
+          <t>-3,59; 0,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,15</t>
+          <t>-1,92; 1,11</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,4</t>
+          <t>-0,81; 3,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,17</t>
+          <t>-3,61; 0,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,18</t>
+          <t>-1,94; 1,14</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-24,42; -0,38</t>
+          <t>-22,03; -0,25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 1,64</t>
+          <t>-6,64; 1,35</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 0,07</t>
+          <t>-11,95; 0,01</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -0,46</t>
+          <t>-27,36; -0,3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 1,88</t>
+          <t>-7,62; 1,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 0,09</t>
+          <t>-14,14; -0,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38C-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-7,8</t>
+          <t>-11,73</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-6,9</t>
+          <t>-9,38</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 2,72</t>
+          <t>-20,59; -0,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 3,89</t>
+          <t>-15,07; 2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -0,26</t>
+          <t>-15,71; -3,04</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-13,85%</t>
+          <t>-20,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-6,82%</t>
+          <t>-9,32%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,34%</t>
+          <t>-15,42%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 5,22</t>
+          <t>-35,53; -1,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 6,09</t>
+          <t>-22,06; 3,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,96; -0,49</t>
+          <t>-24,79; -5,01</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-4,24</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-15,91</t>
+          <t>-6,95</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-9,23</t>
+          <t>-5,3</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 4,27</t>
+          <t>-10,99; 3,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-41,29; -3,87</t>
+          <t>-12,24; -1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,47; -2,07</t>
+          <t>-9,33; -0,53</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-4,31%</t>
+          <t>-6,19%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-19,33%</t>
+          <t>-8,45%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-12,27%</t>
+          <t>-7,05%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 6,67</t>
+          <t>-15,53; 5,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,2; -4,8</t>
+          <t>-14,65; -2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,9; -2,86</t>
+          <t>-12,2; -0,75</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-3,84</t>
+          <t>-6,05</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,32</t>
+          <t>-3,57</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 1,21</t>
+          <t>-10,87; -1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,86</t>
+          <t>-4,85; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,49</t>
+          <t>-6,43; -0,47</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-4,73%</t>
+          <t>-7,46%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-1,04%</t>
+          <t>-1,34%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-2,79%</t>
+          <t>-4,3%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 1,53</t>
+          <t>-12,95; -2,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,54</t>
+          <t>-5,54; 3,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 0,59</t>
+          <t>-7,61; -0,59</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-24,85</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-13,67</t>
+          <t>-0,23</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-61,64; 0,32</t>
+          <t>-5,08; 3,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,15</t>
+          <t>-2,52; 3,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 0,92</t>
+          <t>-2,56; 2,45</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-28,49%</t>
+          <t>-0,95%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-15,4%</t>
+          <t>-0,25%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,04; 0,39</t>
+          <t>-5,61; 3,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 4,72</t>
+          <t>-2,74; 4,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 1,04</t>
+          <t>-2,82; 2,81</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-0,17</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 3,06</t>
+          <t>-4,77; 2,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,56</t>
+          <t>-1,67; 3,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,69</t>
+          <t>-2,32; 2,06</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0,38%</t>
+          <t>-1,4%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>-0,18%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 3,42</t>
+          <t>-5,07; 2,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,9</t>
+          <t>-1,76; 4,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,98</t>
+          <t>-2,48; 2,26</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1,92</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-1,59</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,8</t>
+          <t>-4,73; 0,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,36</t>
+          <t>-2,72; 1,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,47</t>
+          <t>-3,12; 0,15</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1,98%</t>
+          <t>-2,26%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>-1,04%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-0,53%</t>
+          <t>-1,63%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,83</t>
+          <t>-4,82; 0,48</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,46</t>
+          <t>-2,76; 1,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,51</t>
+          <t>-3,22; 0,14</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,78</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,45</t>
+          <t>-1,43; 3,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,84</t>
+          <t>-3,78; 0,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,11</t>
+          <t>-2,21; 0,89</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-1,63%</t>
+          <t>-1,8%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-0,57%</t>
+          <t>-0,8%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,61</t>
+          <t>-1,45; 3,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,86</t>
+          <t>-3,81; 0,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,14</t>
+          <t>-2,24; 0,91</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-6,81</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-0,9</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-1,48</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -0,25</t>
+          <t>-4,14; 0,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,35</t>
+          <t>-2,47; 0,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 0,01</t>
+          <t>-2,84; -0,13</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-8,35%</t>
+          <t>-2,6%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-1,3%</t>
+          <t>-1,03%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-4,6%</t>
+          <t>-1,76%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-27,36; -0,3</t>
+          <t>-5,01; 0,12</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,54</t>
+          <t>-2,79; 0,76</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -0,03</t>
+          <t>-3,35; -0,16</t>
         </is>
       </c>
     </row>
